--- a/docs/downloads/04/tbl_cm_educ_sex_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_sex_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -463,14 +463,8 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>6.7</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -555,37 +549,31 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E9">
-        <v>10.6</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <v>1.8</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -601,14 +589,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="E11">
-        <v>5.6</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12">
@@ -624,14 +612,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D12">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E12">
-        <v>75</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="13">
@@ -647,14 +635,8 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>6</v>
-      </c>
-      <c r="E13">
-        <v>16.7</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -665,19 +647,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E14">
-        <v>2.8</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="15">
@@ -693,14 +675,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D15">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="E15">
-        <v>12.6</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="16">
@@ -716,14 +698,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D16">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E16">
-        <v>44.8</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="17">
@@ -739,37 +721,31 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D17">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E17">
-        <v>33.3</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>8</v>
-      </c>
-      <c r="E18">
-        <v>9.199999999999999</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -785,14 +761,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E19">
-        <v>15.4</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="20">
@@ -808,14 +784,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D20">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>57.7</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="21">
@@ -831,14 +807,8 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>6</v>
-      </c>
-      <c r="E21">
-        <v>23.1</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -849,19 +819,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E22">
-        <v>3.8</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="23">
@@ -877,14 +847,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D23">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="E23">
-        <v>23.4</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="24">
@@ -900,14 +870,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D24">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E24">
-        <v>58.6</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="25">
@@ -923,37 +893,31 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D25">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E25">
-        <v>12.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>6</v>
-      </c>
-      <c r="E26">
-        <v>5.4</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -969,14 +933,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E27">
-        <v>9.1</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="28">
@@ -992,14 +956,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E28">
-        <v>45.5</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="29">
@@ -1015,14 +979,8 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>9</v>
-      </c>
-      <c r="E29">
-        <v>40.9</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1033,19 +991,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E30">
-        <v>4.5</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="31">
@@ -1061,14 +1019,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D31">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="E31">
-        <v>13.8</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="32">
@@ -1084,14 +1042,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D32">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E32">
-        <v>46.8</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="33">
@@ -1107,37 +1065,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D33">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E33">
-        <v>31.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D34">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E34">
-        <v>7.4</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="35">
@@ -1153,14 +1111,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D35">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="E35">
-        <v>11.4</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="36">
@@ -1176,14 +1134,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D36">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="E36">
-        <v>61.4</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="37">
@@ -1199,14 +1157,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D37">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E37">
-        <v>22.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="38">
@@ -1217,19 +1175,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="E38">
-        <v>4.4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
@@ -1245,14 +1203,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D39">
-        <v>67</v>
+        <v>199</v>
       </c>
       <c r="E39">
-        <v>16.5</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="40">
@@ -1268,14 +1226,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D40">
-        <v>199</v>
+        <v>104</v>
       </c>
       <c r="E40">
-        <v>49.1</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="41">
@@ -1291,60 +1249,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D41">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="E41">
-        <v>25.7</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D42">
-        <v>33</v>
-      </c>
-      <c r="E42">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D43">
-        <v>2</v>
-      </c>
-      <c r="E43">
-        <v>0.5</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_cm_educ_sex_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_sex_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,7 +394,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D2">
@@ -483,12 +483,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>15</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -503,14 +497,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D7">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="E7">
-        <v>45.1</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="8">
@@ -526,14 +520,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="E8">
-        <v>27.4</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="9">
@@ -549,31 +543,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>12.4</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Ampijoroa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>14</v>
+      </c>
+      <c r="E10">
+        <v>12.4</v>
       </c>
     </row>
     <row r="11">
@@ -589,14 +589,8 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>27</v>
-      </c>
-      <c r="E11">
-        <v>75</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -612,14 +606,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="E12">
-        <v>16.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -635,8 +629,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
-        </is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>6</v>
+      </c>
+      <c r="E13">
+        <v>16.7</v>
       </c>
     </row>
     <row r="14">
@@ -647,19 +647,13 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>11</v>
-      </c>
-      <c r="E14">
-        <v>12.6</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -675,14 +669,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D15">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E15">
-        <v>44.8</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="16">
@@ -698,14 +692,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D16">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E16">
-        <v>33.3</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="17">
@@ -721,31 +715,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E17">
-        <v>9.199999999999999</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>8</v>
+      </c>
+      <c r="E18">
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -761,14 +761,8 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>15</v>
-      </c>
-      <c r="E19">
-        <v>57.7</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -784,14 +778,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E20">
-        <v>23.1</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="21">
@@ -807,8 +801,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
-        </is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>6</v>
+      </c>
+      <c r="E21">
+        <v>23.1</v>
       </c>
     </row>
     <row r="22">
@@ -819,19 +819,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>24</v>
-      </c>
-      <c r="E22">
-        <v>21.6</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -847,14 +841,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D23">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="E23">
-        <v>58.6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="24">
@@ -870,14 +864,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E24">
-        <v>12.6</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="25">
@@ -893,54 +887,60 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="E25">
-        <v>7.2</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>14</v>
+      </c>
+      <c r="E26">
+        <v>12.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E27">
-        <v>45.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="28">
@@ -956,14 +956,8 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>9</v>
-      </c>
-      <c r="E28">
-        <v>40.9</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -979,8 +973,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
-        </is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>10</v>
+      </c>
+      <c r="E29">
+        <v>45.5</v>
       </c>
     </row>
     <row r="30">
@@ -991,19 +991,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D30">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E30">
-        <v>13.8</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="31">
@@ -1014,19 +1014,13 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>44</v>
-      </c>
-      <c r="E31">
-        <v>46.8</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1042,14 +1036,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D32">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E32">
-        <v>31.9</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="33">
@@ -1065,60 +1059,60 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D33">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E33">
-        <v>7.4</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D34">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E34">
-        <v>11.4</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D35">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="E35">
-        <v>61.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="36">
@@ -1134,14 +1128,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D36">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E36">
-        <v>22.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="37">
@@ -1157,14 +1151,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="E37">
-        <v>4.4</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="38">
@@ -1175,19 +1169,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D38">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="E38">
-        <v>16</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="39">
@@ -1198,19 +1192,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D39">
-        <v>199</v>
+        <v>5</v>
       </c>
       <c r="E39">
-        <v>49.1</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="40">
@@ -1226,14 +1220,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D40">
-        <v>104</v>
+        <v>6</v>
       </c>
       <c r="E40">
-        <v>25.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="41">
@@ -1249,13 +1243,82 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>59</v>
+      </c>
+      <c r="E41">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>199</v>
+      </c>
+      <c r="E42">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>104</v>
+      </c>
+      <c r="E43">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
-      <c r="D41">
+      <c r="D44">
         <v>37</v>
       </c>
-      <c r="E41">
+      <c r="E44">
         <v>9.1</v>
       </c>
     </row>

--- a/docs/downloads/04/tbl_cm_educ_sex_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_sex_marovoay_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -407,7 +407,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -430,7 +430,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -510,7 +510,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -556,7 +556,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -682,7 +682,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -728,7 +728,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -751,7 +751,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -768,7 +768,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -791,7 +791,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -814,7 +814,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -854,7 +854,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -923,7 +923,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1009,7 +1009,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1049,7 +1049,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1118,7 +1118,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1187,7 +1187,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1233,7 +1233,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1256,7 +1256,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1302,7 +1302,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
